--- a/VT_REG1_IND_V12.xlsx
+++ b/VT_REG1_IND_V12.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261020\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261020-v02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA652D2-E860-46CD-B2AC-D008F0956A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526D456-1BB7-4F14-A827-FE14E6E9EF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1539,7 +1539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="212">
   <si>
     <t>CommName</t>
   </si>
@@ -2166,6 +2166,15 @@
   </si>
   <si>
     <t>Demand Technologies Industry Sector - Existing Other Appliance - LPG</t>
+  </si>
+  <si>
+    <t>INDGAS</t>
+  </si>
+  <si>
+    <t>DIOAPP</t>
+  </si>
+  <si>
+    <t>ACT_BND</t>
   </si>
 </sst>
 </file>
@@ -7597,7 +7606,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:U35"/>
+  <dimension ref="B1:U41"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -7786,9 +7795,8 @@
         <v>85</v>
       </c>
       <c r="N6" s="111"/>
-      <c r="O6" s="107" t="str">
-        <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$21</f>
-        <v>DIOAPP</v>
+      <c r="O6" s="107" t="s">
+        <v>210</v>
       </c>
       <c r="P6" s="107" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$21</f>
@@ -7988,7 +7996,7 @@
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="118" t="s">
-        <v>35</v>
+        <v>211</v>
       </c>
       <c r="M15" s="108" t="s">
         <v>11</v>
@@ -8644,15 +8652,48 @@
       <c r="J32" s="102"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>176</v>
+      </c>
       <c r="E35" s="7"/>
       <c r="L35" s="1"/>
+    </row>
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>177</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
